--- a/Assessment Questions/CDE/Big Data Advance/Mini Project Flow/Creating an HDFS cluster with containers/HDFS_Cluster_Questions.xlsx
+++ b/Assessment Questions/CDE/Big Data Advance/Mini Project Flow/Creating an HDFS cluster with containers/HDFS_Cluster_Questions.xlsx
@@ -7,7 +7,7 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Questions" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="questions" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -439,7 +439,7 @@
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>Answer</t>
+          <t>Question Type</t>
         </is>
       </c>
     </row>
@@ -464,7 +464,7 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Docker</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -514,7 +514,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -539,7 +539,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>More DataNodes</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -564,7 +564,7 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -589,7 +589,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>hdfs dfs -ls</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -614,7 +614,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -639,7 +639,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Data replication handles fault tolerance</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -689,7 +689,7 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>hdfs-site.xml</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -714,7 +714,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -739,7 +739,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Containers</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -764,7 +764,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -789,7 +789,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Block</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -814,7 +814,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -839,7 +839,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>Secondary/Standby NameNode</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
@@ -864,7 +864,7 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>B</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -889,7 +889,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>hdfs dfs -put</t>
+          <t>Short Answer</t>
         </is>
       </c>
     </row>
@@ -914,7 +914,7 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>A</t>
+          <t>MCQ</t>
         </is>
       </c>
     </row>
@@ -939,7 +939,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Docker Compose</t>
+          <t>Scenario-Based</t>
         </is>
       </c>
     </row>
